--- a/jogos_2024-09-17.xlsx
+++ b/jogos_2024-09-17.xlsx
@@ -1149,26 +1149,26 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>14</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>6.5</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>1.15</v>
+        <v>4.75</v>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>2.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.53</v>
+        <v>4.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="U6" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.41</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>4.4</v>
+        <v>1.18</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.3</v>
+        <v>1.44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.22</v>
+        <v>3</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45552.47916666666</v>
@@ -1278,26 +1278,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.6</v>
+        <v>14</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="N7" t="n">
-        <v>4.75</v>
+        <v>1.15</v>
       </c>
       <c r="O7" t="n">
+        <v>10</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2.2</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD7" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.18</v>
+        <v>4.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.44</v>
+        <v>4.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3</v>
+        <v>1.22</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45552.47916666666</v>
@@ -1933,109 +1933,109 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>3</v>
       </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
       <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
         <v>2</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.78</v>
+        <v>4.57</v>
       </c>
       <c r="M12" t="n">
-        <v>4.16</v>
+        <v>4.36</v>
       </c>
       <c r="N12" t="n">
-        <v>4.73</v>
+        <v>1.76</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.5</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X12" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.85</v>
-      </c>
       <c r="Z12" t="n">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.84</v>
+        <v>2.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['21', '27', '52']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['27', '38', '86']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>2.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.19</v>
+        <v>1.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.75</v>
+        <v>1.44</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45552.57291666666</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.57</v>
+        <v>1.78</v>
       </c>
       <c r="M13" t="n">
-        <v>4.36</v>
+        <v>4.16</v>
       </c>
       <c r="N13" t="n">
-        <v>1.76</v>
+        <v>4.73</v>
       </c>
       <c r="O13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q13" t="n">
         <v>4.5</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.2</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="X13" t="n">
-        <v>5.6</v>
+        <v>4.35</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['21', '27', '52']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>['27', '38', '86']</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI13" t="n">
+      <c r="AJ13" t="n">
         <v>2.75</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.44</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45552.57291666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>SuperSport United</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.55</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.45</v>
+        <v>6.1</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.33</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.5</v>
       </c>
       <c r="V17" t="n">
         <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="X17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA17" t="n">
         <v>4.2</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['10', '28', '71']</t>
+          <t>['62', '65']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['90+7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.48</v>
+        <v>1.05</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>2.6</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.05</v>
+        <v>1.33</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45552.60416666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.25</v>
+        <v>2.55</v>
       </c>
       <c r="M18" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['10', '28', '71']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>['90+7']</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.48</v>
       </c>
-      <c r="O18" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X18" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['23', '42']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.14</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45552.60416666666</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SuperSport United</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>5.25</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="N19" t="n">
-        <v>6.1</v>
+        <v>1.48</v>
       </c>
       <c r="O19" t="n">
-        <v>2.05</v>
+        <v>5.88</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>1.98</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>3.25</v>
+        <v>2.43</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['23', '42']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.4</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['62', '65']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>4</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45552.60416666666</v>
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.75</v>
+        <v>3.8</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="O24" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q24" t="n">
-        <v>1.95</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="U24" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X24" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.89</v>
+        <v>2.25</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75', '90+6']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '69']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45552.65625</v>
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="O25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="T25" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="X25" t="n">
-        <v>4.33</v>
+        <v>3.48</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.25</v>
+        <v>2.01</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['75', '90+6']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['9', '69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45552.65625</v>
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.7</v>
+        <v>2.15</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.8</v>
       </c>
-      <c r="O26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X26" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Y26" t="n">
+      <c r="Z26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC26" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AD26" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '15', '90+1', '90+6']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.91</v>
+        <v>1.35</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.41</v>
+        <v>1.81</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45552.65625</v>
@@ -3858,35 +3858,35 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.09</v>
       </c>
       <c r="N27" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="O27" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>4.21</v>
       </c>
       <c r="R27" t="n">
         <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="T27" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="U27" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X27" t="n">
-        <v>3.8</v>
+        <v>3.59</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Z27" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['2', '15', '90+1', '90+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.16</v>
+        <v>2.5</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45552.65625</v>
@@ -3997,16 +3997,16 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Loughgall</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.5</v>
+        <v>1.38</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>1.9</v>
+        <v>6.25</v>
       </c>
       <c r="O28" t="n">
-        <v>4.1</v>
+        <v>1.73</v>
       </c>
       <c r="P28" t="n">
-        <v>2.16</v>
+        <v>2.63</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.44</v>
+        <v>6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>2.99</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.66</v>
+        <v>2.08</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
-        <v>3.48</v>
+        <v>6.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.93</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['5', '53']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AI28" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['39']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>1.66</v>
+        <v>3.14</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45552.65625</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.09</v>
+        <v>3.7</v>
       </c>
       <c r="M29" t="n">
-        <v>3.09</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
-        <v>2.94</v>
+        <v>1.8</v>
       </c>
       <c r="O29" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.21</v>
+        <v>2.27</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>3.06</v>
+        <v>3.32</v>
       </c>
       <c r="T29" t="n">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="U29" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="V29" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="X29" t="n">
-        <v>3.59</v>
+        <v>4.25</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.14</v>
+        <v>2.48</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.78</v>
+        <v>1.22</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.67</v>
+        <v>2.41</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45552.65625</v>
@@ -4255,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Loughgall</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4281,65 +4281,65 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.38</v>
+        <v>5.75</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N30" t="n">
-        <v>6.25</v>
+        <v>1.44</v>
       </c>
       <c r="O30" t="n">
-        <v>1.73</v>
+        <v>5.75</v>
       </c>
       <c r="P30" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>4.3</v>
+        <v>3.32</v>
       </c>
       <c r="T30" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="U30" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="V30" t="n">
         <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X30" t="n">
-        <v>6.5</v>
+        <v>4.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>2</v>
+        <v>2.57</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['5', '53']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.07</v>
+        <v>2.7</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.88</v>
+        <v>1.13</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.33</v>
+        <v>3.1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.14</v>
+        <v>1.42</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45552.65625</v>
@@ -4384,22 +4384,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="M31" t="n">
-        <v>9.15</v>
+        <v>6.24</v>
       </c>
       <c r="N31" t="n">
-        <v>18</v>
+        <v>9.65</v>
       </c>
       <c r="O31" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="P31" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="Q31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S31" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="T31" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="U31" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="V31" t="n">
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>8.199999999999999</v>
+        <v>6.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['19', '33', '38', '57', '61', '73', '78', '85', '90+2']</t>
+          <t>['46', '83', '90+5']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['49', '50']</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AH31" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AJ31" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45552.66666666666</v>
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
         <v>3</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>1</v>
       </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.33</v>
+        <v>3.12</v>
       </c>
       <c r="M33" t="n">
-        <v>6.24</v>
+        <v>3.9</v>
       </c>
       <c r="N33" t="n">
-        <v>9.65</v>
+        <v>2.28</v>
       </c>
       <c r="O33" t="n">
-        <v>1.67</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="R33" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="S33" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="T33" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="U33" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W33" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="X33" t="n">
-        <v>6.05</v>
+        <v>4.7</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['46', '83', '90+5']</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['68']</t>
+          <t>['23', '41', '67']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.05</v>
+        <v>1.94</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.8</v>
+        <v>1.28</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.22</v>
+        <v>2.5</v>
       </c>
       <c r="AJ33" t="n">
-        <v>4</v>
+        <v>1.53</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45552.66666666666</v>
@@ -4771,109 +4771,109 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
         <v>3</v>
       </c>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M34" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="N34" t="n">
+        <v>18</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>10</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X34" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB34" t="n">
         <v>2</v>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O34" t="n">
-        <v>4</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AC34" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['3']</t>
+          <t>['19', '33', '38', '57', '61', '73', '78', '85', '90+2']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['23', '41', '67']</t>
+          <t>['49', '50']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.28</v>
+        <v>5.7</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.5</v>
+        <v>1.17</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.53</v>
+        <v>4.75</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45552.66666666666</v>
@@ -5287,22 +5287,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ituano</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -5313,65 +5313,65 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.38</v>
+        <v>1.73</v>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N38" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="O38" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="P38" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="R38" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="S38" t="n">
-        <v>2.23</v>
+        <v>2.48</v>
       </c>
       <c r="T38" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="U38" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="V38" t="n">
         <v>1.1</v>
       </c>
       <c r="W38" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X38" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AA38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['24', '45']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -5380,16 +5380,16 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45552.89583333334</v>
@@ -5416,22 +5416,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ituano</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -5442,65 +5442,65 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="M39" t="n">
+        <v>3</v>
+      </c>
+      <c r="N39" t="n">
         <v>3.1</v>
       </c>
-      <c r="N39" t="n">
-        <v>4.5</v>
-      </c>
       <c r="O39" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="P39" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="R39" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="S39" t="n">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="T39" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="U39" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="V39" t="n">
         <v>1.1</v>
       </c>
       <c r="W39" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X39" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="Z39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD39" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA39" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['24', '45']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AJ39" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45552.89583333334</v>
